--- a/data/dhathri_jobs.xlsx
+++ b/data/dhathri_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 05:09:16</t>
+          <t>2026-09-03 07:12:18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 05:09:16</t>
+          <t>2026-09-03 07:12:18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 05:09:16</t>
+          <t>2026-09-03 07:12:18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/data/dhathri_jobs.xlsx
+++ b/data/dhathri_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 07:12:18</t>
+          <t>2026-09-03 07:32:25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 07:12:18</t>
+          <t>2026-09-03 07:32:25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 07:12:18</t>
+          <t>2026-09-03 07:32:25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/data/dhathri_jobs.xlsx
+++ b/data/dhathri_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 07:32:25</t>
+          <t>2026-09-03 08:49:24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 07:32:25</t>
+          <t>2026-09-03 08:49:24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 07:32:25</t>
+          <t>2026-09-03 08:49:24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/data/dhathri_jobs.xlsx
+++ b/data/dhathri_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 08:49:24</t>
+          <t>2026-09-03 09:26:18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 08:49:24</t>
+          <t>2026-09-03 09:26:18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 08:49:24</t>
+          <t>2026-09-03 09:26:18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/data/dhathri_jobs.xlsx
+++ b/data/dhathri_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:18</t>
+          <t>2026-09-03 09:50:18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:18</t>
+          <t>2026-09-03 09:50:18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:18</t>
+          <t>2026-09-03 09:50:18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/data/dhathri_jobs.xlsx
+++ b/data/dhathri_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:18</t>
+          <t>2026-09-03 12:40:06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:18</t>
+          <t>2026-09-03 12:40:06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:18</t>
+          <t>2026-09-03 12:40:06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -705,6 +705,1000 @@
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cc65b2d7e8cd0ca2e42c</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3 KUBED CONSULTING INDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer Dear Candidate Greetings from 3 Kubed Consulting India Pvt Ltd We are seeking aCloud Engineer with AI MLexpertise to design build and support intelligent applications usingAzure Services Azure AI Foundry Docker and Kubernetes services This is for one of our prestigious clients f</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5823128806?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>eb766d663d9c0ae14e58</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>30</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>skill:Azure, skill:Docker, skill:Kubernetes</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3f74c38a88f9a865435d</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Public Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Description Change the world. Love your job. Texas Instruments is seeking a skilled Public Cloud Engineer to implement, automate, and operate the enterprise public cloud platform across AWS (primary), Azure, and GCP. This role partners with the Public Cloud Architect to execute on platform strategy </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5830626894?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>45f36ed761a638b42eff</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>50</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>skill:Azure, skill:Kubernetes, skill:Terraform, skill:CI/CD, skill:GCP</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0fa3d588c2f7472524a1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tekskills India Private Limited</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>We are hiring an experienced Platform Engineer with strong expertise in Cloudera, Kafka, Databricks, Azure Synapse, PySpark, and Infrastructure Automation . Mandatory Skills Cloudera Platform Administration Cloudera Hadoop Administration Kafka Cluster Administration &amp; Maintenance Databricks Apache I</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5804149618?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>274b5127202b71d7582d</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>skill:Azure, skill:Docker, skill:Kubernetes, skill:Ansible, skill:Terraform, skill:Troubleshooting</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ad3b29b4786c6e25b08f</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aliqan Services</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Must have- 1. AWS/Azure(Any one cloud). 2.Ansible / Terraform. 3.Java. 4.Maria DB / MySql. RESPONSIBILITIES:- Site Reliability Engineer - PRIMARY RESPONSIBILITIES OF THIS POSITION SRE team members triage and solve escalations from our care team. This can require debugging production services, invest</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5794938989?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4fd31e180a810aee1d13</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>50</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>skill:Java, skill:Azure, skill:Ansible, skill:Terraform, skill:MySQL</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>e3e350c49aa1947cf512</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ather Energy</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Collaborate with engineering and development teams to evaluate and identify optimal cloud solutions Work on the GCP Kubernetes cluster for upgrades, migration, and troubleshooting. Maintain the Kafka cluster and Devtron CICD tool, and improve productivity by addressing the technical challenges encou</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5832796606?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>33c32c32f78c540a16b4</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>30</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>skill:Kubernetes, skill:Troubleshooting, skill:GCP</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>79a8f5f792ec2476bf6c</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WorkSpan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Job Brief: Multi-Cloud SRE / DevOps Engineer We are seeking a versatile Multi-Cloud Site Reliability / DevOps Engineer to design, automate, and maintain our geographically distributed infrastructure across Amazon Web Services (AWS), Google Cloud Platform (GCP), and Microsoft Azure. In this role, you</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5833586720?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>c2e2e6c5e73113fbb8ca</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>skill:Azure, skill:GCP</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>441a5d0897b1a1836cc5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Healthifyme</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Requirements Design, write and build tools to improve the reliability, latency, availability and scalability of HealthifyMe application. Communicate, collaborate and work effectively across distributed teams in a global environment Optimize performance and solve issues across the entire stack: hardw</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/1404486131?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>a6eab982e4ca15634a20</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>20</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>skill:Ansible, skill:Terraform</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>bbc336360507e6c53380</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Beiing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>What you’ll do • Develop and Maintain IAC using Terraform and Ansible • Draft design documents that translate requirements into code. • Deal with challenges associated with scale. • Assume responsibilities from technical design through technical client support. • Manage expectations with internal st</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/1549938778?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1c9f246c63c4bd0312e8</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>skill:Ansible, skill:Terraform</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>f5d403ed720a472c876b</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Wissen Technology</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2 years of hands-on experience in Java development. Strong knowledge of Boto3/Boto AWS libraries (Python). Solid experience with AWS services: EC2, ELB/ALB, CloudWatch. Familiarity with SRE practices and maintenance processes. Strong experience in debugging, troubleshooting, and unit testing. Profic</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5211779025?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>03ea2a71e141f631af37</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>40</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>skill:Java, skill:Git, skill:CI/CD, skill:Troubleshooting</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1e8d90b2f7b27eec4aee</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Wissen Technology</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SRE Engineer</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Job Description. 1. Cloud experience (Any cloud is fine although AWS is preferred. If non-AWS cloud, then the experience should reflect familiarity with the cloud's common services) 2. Good grasp of Scripting (in Linux for sure ie bash/sh/zsh etc, Windows : nice to have) 3. Python or Java or JS basi</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5501134569?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>32b60b6a0297c5084f53</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>60</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>skill:Java, skill:Docker, skill:Linux, skill:Terraform, skill:Logging, skill:Monitoring</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0d112f518f8db899e3c6</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jobdost</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SRE Devops</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Candidates MUST HAVE : Experience with Infrastructure-as-Code tools(IaS) like Terraform and Cloud Formation. Proficiency in cloud-native technologies and architectures (Docker/ Kubernetes), Ci/CD pipelines. Good experience in Javascript. Expertise in Linux / Windows environment. Good Experience in S</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/4344577925?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>08c477bc04ba32062d49</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>60</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>skill:Docker, skill:Kubernetes, skill:Linux, skill:Git, skill:Terraform, skill:CI/CD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0e6b548516e16807909f</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wissen Technology</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Devops/ SRE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>The candidate should have a background in development/programming with experience in at least one of the following: .NET, Java (Spring Boot), ReactJS, or AngularJS. Primary Skills: AWS or GCP Cloud DevOps CI/CD pipelines (e.g., Azure DevOps, Jenkins) Python/Bash/PowerShell scripting Secondary Skills</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5211779221?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>48fe7642ecb269a15f16</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>70</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>skill:Java, skill:Azure, skill:Docker, skill:Kubernetes, skill:Jenkins, skill:CI/CD, skill:GCP</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>b0b40da0f0507f0bd627</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Multi Recruit</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sr. Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Support for Incident and Request management tasks as assigned. Administration and understanding of the following network services to support Incident and Request tasks as assigned: Palo Alto Firewalls LAN Routing and Switching Microsoft Azure Networking – Vnets, Express Route, Vnet Peering, VPN Gate</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/2853928191?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bf7b45d8e0f16436c56c</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>skill:Azure, skill:Monitoring</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>eb302cdce845b1a9e376</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Jobdost</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>What does the role look like? Software Development Engineers will be responsible to participate in all stages of the software product development life cycle. This will include analyzing system and user requirements, designing software flowcharts, writing clean Java code, troubleshooting bugs, and ru</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/4344578477?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:40:06</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>7abf64856830eacb607b</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>20</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>skill:Java, skill:Troubleshooting</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/dhathri_jobs.xlsx
+++ b/data/dhathri_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 12:40:06</t>
+          <t>2026-09-03 13:20:27</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">

--- a/data/dhathri_jobs.xlsx
+++ b/data/dhathri_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 13:20:27</t>
+          <t>2026-09-03 14:43:51</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">

--- a/data/dhathri_jobs.xlsx
+++ b/data/dhathri_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 14:43:51</t>
+          <t>2026-09-03 16:31:36</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">

--- a/data/dhathri_jobs.xlsx
+++ b/data/dhathri_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 16:31:36</t>
+          <t>2026-09-04 02:29:17</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">

--- a/data/dhathri_jobs.xlsx
+++ b/data/dhathri_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,77 @@
           <t>Notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>df154693f3b7f3fc9fa2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Job Description: Java Full Stack Developer (React.js &amp; Azure) Job Summary We are seeking a highly skilled Java Full Stack Developer with proven expertise in building robust backend services using Java/Spring Boot , developing dynamic user interfaces with React.js , and deploying scalable application</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5876028775?se=VgUxE2as8RGnuL6Fc8YS3w&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=856CDB2255452987D90E6BE969C4268474A3A29E</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:50:05</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:50:05</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>61b0829734ac4f5c1943</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>skill:Java, skill:Azure</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/dhathri_jobs.xlsx
+++ b/data/dhathri_jobs.xlsx
@@ -496,60 +496,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>df154693f3b7f3fc9fa2</t>
+          <t>b089a3cfab02f278c172</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>capco</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+          <t>QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Job Description: Java Full Stack Developer (React.js &amp; Azure) Job Summary We are seeking a highly skilled Java Full Stack Developer with proven expertise in building robust backend services using Java/Spring Boot , developing dynamic user interfaces with React.js , and deploying scalable application</t>
+          <t>&amp;lt;h3&amp;gt;Shape the Future of Financial Services with Capco&amp;lt;/h3&amp;gt;
+&amp;lt;p&amp;gt;At Capco, we specialize in management consulting and software development, partnering with leading international banks and insurance companies across Western Europe. Our innovative approach and collaborative culture make</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876028775?se=VgUxE2as8RGnuL6Fc8YS3w&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=856CDB2255452987D90E6BE969C4268474A3A29E</t>
+          <t>https://www.arbeitnow.com/jobs/companies/capco/qa-automation-engineer-118845</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>arbeitnow</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-09 15:50:05</t>
+          <t>2026-09-10 15:44:54</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-09 15:50:05</t>
+          <t>2026-09-10 15:44:54</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>61b0829734ac4f5c1943</t>
+          <t>b170f1c2eea6a07ed122</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>skill:Java, skill:Azure</t>
+          <t>skill:Java, skill:Git, skill:Jenkins, skill:CI/CD, skill:Jira</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/data/dhathri_jobs.xlsx
+++ b/data/dhathri_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,74 +492,6 @@
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>b089a3cfab02f278c172</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>capco</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>&amp;lt;h3&amp;gt;Shape the Future of Financial Services with Capco&amp;lt;/h3&amp;gt;
-&amp;lt;p&amp;gt;At Capco, we specialize in management consulting and software development, partnering with leading international banks and insurance companies across Western Europe. Our innovative approach and collaborative culture make</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/capco/qa-automation-engineer-118845</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>arbeitnow</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:44:54</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:44:54</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>b170f1c2eea6a07ed122</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>50</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>skill:Java, skill:Git, skill:Jenkins, skill:CI/CD, skill:Jira</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
